--- a/Codelist Excel Files and Conversion Templates to XML/safetyFormat.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/safetyFormat.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming the design approach and partial-factor framework a rigid inclusion design applies. Used for the value of the safetyFormat property of diggs:RISystemBasis. RI_Design_Parameter_Analysis.md Group A row 8 names four frameworks in current practice; the list is open.</t>
+          <t>Codes naming the design approach and partial-factor framework a rigid inclusion design applies. Used for the value of the safetyFormat property of diggs:RIProgramBasis. RI_Design_Parameter_Analysis.md Group A row 8 names four frameworks in current practice; the list is open.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:safetyFormat</t>
+          <t>//diggs:RIProgramBasis/diggs:safetyFormat</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:safetyFormat</t>
+          <t>//diggs:RIProgramBasis/diggs:safetyFormat</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:safetyFormat</t>
+          <t>//diggs:RIProgramBasis/diggs:safetyFormat</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:safetyFormat</t>
+          <t>//diggs:RIProgramBasis/diggs:safetyFormat</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:safetyFormat</t>
+          <t>//diggs:RIProgramBasis/diggs:safetyFormat</t>
         </is>
       </c>
     </row>
